--- a/site/StructureDefinition-hcen-motivo-consulta.xlsx
+++ b/site/StructureDefinition-hcen-motivo-consulta.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -777,9 +777,6 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>section/entry/observation/code/@displayName</t>
-  </si>
-  <si>
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
@@ -875,7 +872,7 @@
 </t>
   </si>
   <si>
-    <t>Código que identifica el motivo de la consulta (SNOMED CT u otra terminología)</t>
+    <t>Código que identifica el motivo de la consulta (SNOMED CT u otra terminología, p.ej. un tesauro clínico institucional)</t>
   </si>
   <si>
     <t>0..1 to account for primarily narrative only resources.</t>
@@ -928,6 +925,12 @@
   </si>
   <si>
     <t>Condition.code.coding</t>
+  </si>
+  <si>
+    <t>Slicing abierto por system: además del slice snomed, admite otra codificación con su propio system — p.ej. un código de un tesauro clínico (ver sección 4.7.4 Tesauro clínico)</t>
+  </si>
+  <si>
+    <t>El slicing es abierto por system. Además del slice snomed, se puede incluir una codificación adicional de otro vocabulario — p.ej. un código de un tesauro clínico (ver [Tesauro clínico](hcen-terminologia.html#tesauro-clínico), sección 4.7.4). La URI de ese system depende de la institución de origen y su confirmación es externa a esta guía; no se fija ni se valida en este perfil.</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -4554,19 +4557,19 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4577,10 +4580,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4603,19 +4606,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4664,7 +4667,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4688,10 +4691,10 @@
         <v>20</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4702,10 +4705,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4731,16 +4734,16 @@
         <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4789,7 +4792,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4813,10 +4816,10 @@
         <v>20</v>
       </c>
       <c r="AN25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4827,10 +4830,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4856,13 +4859,13 @@
         <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4891,10 +4894,10 @@
         <v>115</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4912,7 +4915,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4933,31 +4936,31 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4979,14 +4982,14 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5011,14 +5014,14 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>280</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
       </c>
@@ -5035,7 +5038,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5047,36 +5050,36 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AK27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AP27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5194,10 +5197,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5317,10 +5320,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5346,10 +5349,10 @@
         <v>205</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>206</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>208</v>
@@ -5392,7 +5395,7 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
@@ -5440,13 +5443,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -5471,10 +5474,10 @@
         <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>208</v>
@@ -5544,7 +5547,7 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -5567,10 +5570,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5688,10 +5691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5811,10 +5814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5856,7 +5859,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>20</v>
@@ -5913,7 +5916,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -5936,10 +5939,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6059,10 +6062,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6124,7 +6127,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6157,7 +6160,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -6180,10 +6183,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6209,10 +6212,10 @@
         <v>193</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
@@ -6280,7 +6283,7 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -6289,10 +6292,10 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>20</v>
@@ -6303,10 +6306,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6329,19 +6332,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6390,7 +6393,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6414,10 +6417,10 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>20</v>
@@ -6428,10 +6431,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6457,16 +6460,16 @@
         <v>193</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6515,7 +6518,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6539,10 +6542,10 @@
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -6553,10 +6556,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6582,13 +6585,13 @@
         <v>157</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6614,13 +6617,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6638,7 +6641,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6659,31 +6662,31 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6702,17 +6705,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6761,7 +6764,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>91</v>
@@ -6776,22 +6779,22 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>20</v>
@@ -6799,10 +6802,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6825,16 +6828,16 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6884,7 +6887,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6902,19 +6905,19 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>20</v>
@@ -6922,10 +6925,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6948,16 +6951,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7007,7 +7010,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7025,19 +7028,19 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>20</v>
@@ -7045,10 +7048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7071,16 +7074,16 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7130,7 +7133,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7139,7 +7142,7 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>103</v>
@@ -7157,10 +7160,10 @@
         <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>20</v>
@@ -7168,10 +7171,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7194,13 +7197,13 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7251,7 +7254,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7275,13 +7278,13 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>20</v>
@@ -7289,10 +7292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7315,13 +7318,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7372,7 +7375,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7399,10 +7402,10 @@
         <v>20</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>20</v>
@@ -7410,10 +7413,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7436,13 +7439,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7493,7 +7496,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7517,13 +7520,13 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>20</v>
@@ -7531,10 +7534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7557,13 +7560,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7614,7 +7617,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7626,7 +7629,7 @@
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7641,7 +7644,7 @@
         <v>20</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -7652,10 +7655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7773,10 +7776,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7896,14 +7899,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7925,16 +7928,16 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7983,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8021,10 +8024,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8050,10 +8053,10 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8080,13 +8083,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8104,7 +8107,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8113,7 +8116,7 @@
         <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -8125,13 +8128,13 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>20</v>
@@ -8142,10 +8145,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8168,13 +8171,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8225,7 +8228,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8234,7 +8237,7 @@
         <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>103</v>
@@ -8252,7 +8255,7 @@
         <v>20</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -8263,10 +8266,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8292,10 +8295,10 @@
         <v>157</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8322,13 +8325,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8346,7 +8349,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8373,7 +8376,7 @@
         <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>20</v>
@@ -8384,10 +8387,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8410,16 +8413,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8469,7 +8472,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8481,7 +8484,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8496,7 +8499,7 @@
         <v>20</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>20</v>
@@ -8507,10 +8510,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8628,10 +8631,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8751,14 +8754,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8780,16 +8783,16 @@
         <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>140</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8838,7 +8841,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8876,10 +8879,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8905,10 +8908,10 @@
         <v>157</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8935,13 +8938,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8959,7 +8962,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8968,7 +8971,7 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>103</v>
@@ -8977,7 +8980,7 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>188</v>
@@ -8986,10 +8989,10 @@
         <v>20</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>20</v>
@@ -8997,10 +9000,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9023,13 +9026,13 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9080,7 +9083,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9089,7 +9092,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9107,10 +9110,10 @@
         <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>20</v>
@@ -9118,10 +9121,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9144,13 +9147,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9201,7 +9204,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9219,16 +9222,16 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
